--- a/survey_templates/043_nonprofit_advocacy_strategy_feedback_evaluation_form--survey_templates.xlsx
+++ b/survey_templates/043_nonprofit_advocacy_strategy_feedback_evaluation_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -715,8 +715,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -744,12 +744,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'executive_director'}</t>
+          <t>executive_director</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Executive Director'}</t>
+          <t>Executive Director</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'program_director'}</t>
+          <t>program_director</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Program Director'}</t>
+          <t>Program Director</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'community_coordinator'}</t>
+          <t>community_coordinator</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Community Coordinator'}</t>
+          <t>Community Coordinator</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'community_development'}</t>
+          <t>community_development</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Community Development'}</t>
+          <t>Community Development</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'advocacy'}</t>
+          <t>advocacy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Advocacy'}</t>
+          <t>Advocacy</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'education'}</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Education'}</t>
+          <t>Education</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'in-person_meetings'}</t>
+          <t>in-person_meetings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'In-person meetings'}</t>
+          <t>In-person meetings</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'email_campaigns'}</t>
+          <t>email_campaigns</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Email campaigns'}</t>
+          <t>Email campaigns</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'increased_public_awareness'}</t>
+          <t>increased_public_awareness</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Increased public awareness'}</t>
+          <t>Increased public awareness</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'policy_changes'}</t>
+          <t>policy_changes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Policy changes'}</t>
+          <t>Policy changes</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'community_engagement'}</t>
+          <t>community_engagement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Community engagement'}</t>
+          <t>Community engagement</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'effective'}</t>
+          <t>effective</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Effective'}</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'ineffective'}</t>
+          <t>ineffective</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Ineffective'}</t>
+          <t>Ineffective</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Not sure'}</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
